--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/accounadjustmanage/assetbookparameter/ValAssetBookParameter.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/accounadjustmanage/assetbookparameter/ValAssetBookParameter.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\assetbookparameter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\开发项目\VAS\code\tams-valuation\src\main\resources\tpl\accounadjustmanage\assetbookparameter\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>账套代码</t>
   </si>
@@ -37,6 +37,10 @@
   </si>
   <si>
     <t>参数说明</t>
+  </si>
+  <si>
+    <t>参数类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -384,21 +388,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="15.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.625" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="6.375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="13.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="6.375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -415,13 +420,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
